--- a/artfynd/A 12081-2024 artfynd.xlsx
+++ b/artfynd/A 12081-2024 artfynd.xlsx
@@ -1288,12 +1288,7 @@
         <v>74153941</v>
       </c>
       <c r="B7" t="n">
-        <v>101680</v>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>104048</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1325,10 +1320,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>541873.0038059668</v>
+        <v>541873</v>
       </c>
       <c r="R7" t="n">
-        <v>6409930.357104327</v>
+        <v>6409930</v>
       </c>
       <c r="S7" t="n">
         <v>50</v>
@@ -1358,19 +1353,9 @@
           <t>2002-08-10</t>
         </is>
       </c>
-      <c r="Z7" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA7" t="inlineStr">
         <is>
           <t>2002-08-10</t>
-        </is>
-      </c>
-      <c r="AB7" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AC7" t="inlineStr">
@@ -1414,12 +1399,7 @@
         <v>74116534</v>
       </c>
       <c r="B8" t="n">
-        <v>101323</v>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>103672</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1451,10 +1431,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>541873.0038059668</v>
+        <v>541873</v>
       </c>
       <c r="R8" t="n">
-        <v>6409930.357104327</v>
+        <v>6409930</v>
       </c>
       <c r="S8" t="n">
         <v>50</v>
@@ -1484,19 +1464,9 @@
           <t>2002-08-10</t>
         </is>
       </c>
-      <c r="Z8" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA8" t="inlineStr">
         <is>
           <t>2002-08-10</t>
-        </is>
-      </c>
-      <c r="AB8" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AC8" t="inlineStr">
@@ -1540,12 +1510,7 @@
         <v>74512145</v>
       </c>
       <c r="B9" t="n">
-        <v>103088</v>
-      </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>105461</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1577,10 +1542,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>541873.0038059668</v>
+        <v>541873</v>
       </c>
       <c r="R9" t="n">
-        <v>6409930.357104327</v>
+        <v>6409930</v>
       </c>
       <c r="S9" t="n">
         <v>50</v>
@@ -1610,19 +1575,9 @@
           <t>2002-08-10</t>
         </is>
       </c>
-      <c r="Z9" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA9" t="inlineStr">
         <is>
           <t>2002-08-10</t>
-        </is>
-      </c>
-      <c r="AB9" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AC9" t="inlineStr">
@@ -1666,12 +1621,7 @@
         <v>74566796</v>
       </c>
       <c r="B10" t="n">
-        <v>96356</v>
-      </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>98611</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1703,10 +1653,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>541873.0038059668</v>
+        <v>541873</v>
       </c>
       <c r="R10" t="n">
-        <v>6409930.357104327</v>
+        <v>6409930</v>
       </c>
       <c r="S10" t="n">
         <v>50</v>
@@ -1736,19 +1686,9 @@
           <t>2002-08-10</t>
         </is>
       </c>
-      <c r="Z10" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA10" t="inlineStr">
         <is>
           <t>2002-08-10</t>
-        </is>
-      </c>
-      <c r="AB10" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AC10" t="inlineStr">
@@ -1792,12 +1732,7 @@
         <v>75155258</v>
       </c>
       <c r="B11" t="n">
-        <v>99566</v>
-      </c>
-      <c r="C11" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>101853</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1829,10 +1764,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>541873.0038059668</v>
+        <v>541873</v>
       </c>
       <c r="R11" t="n">
-        <v>6409930.357104327</v>
+        <v>6409930</v>
       </c>
       <c r="S11" t="n">
         <v>50</v>
@@ -1862,19 +1797,9 @@
           <t>2002-08-10</t>
         </is>
       </c>
-      <c r="Z11" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA11" t="inlineStr">
         <is>
           <t>2002-08-10</t>
-        </is>
-      </c>
-      <c r="AB11" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AC11" t="inlineStr">

--- a/artfynd/A 12081-2024 artfynd.xlsx
+++ b/artfynd/A 12081-2024 artfynd.xlsx
@@ -1288,7 +1288,7 @@
         <v>74153941</v>
       </c>
       <c r="B7" t="n">
-        <v>104048</v>
+        <v>104057</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1399,7 +1399,7 @@
         <v>74116534</v>
       </c>
       <c r="B8" t="n">
-        <v>103672</v>
+        <v>103680</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1510,7 +1510,7 @@
         <v>74512145</v>
       </c>
       <c r="B9" t="n">
-        <v>105461</v>
+        <v>105470</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1621,7 +1621,7 @@
         <v>74566796</v>
       </c>
       <c r="B10" t="n">
-        <v>98611</v>
+        <v>98614</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1732,7 +1732,7 @@
         <v>75155258</v>
       </c>
       <c r="B11" t="n">
-        <v>101853</v>
+        <v>101859</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>

--- a/artfynd/A 12081-2024 artfynd.xlsx
+++ b/artfynd/A 12081-2024 artfynd.xlsx
@@ -1288,7 +1288,7 @@
         <v>74153941</v>
       </c>
       <c r="B7" t="n">
-        <v>104057</v>
+        <v>104060</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1399,7 +1399,7 @@
         <v>74116534</v>
       </c>
       <c r="B8" t="n">
-        <v>103680</v>
+        <v>103682</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1510,7 +1510,7 @@
         <v>74512145</v>
       </c>
       <c r="B9" t="n">
-        <v>105470</v>
+        <v>105473</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1621,7 +1621,7 @@
         <v>74566796</v>
       </c>
       <c r="B10" t="n">
-        <v>98614</v>
+        <v>98615</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1732,7 +1732,7 @@
         <v>75155258</v>
       </c>
       <c r="B11" t="n">
-        <v>101859</v>
+        <v>101860</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>

--- a/artfynd/A 12081-2024 artfynd.xlsx
+++ b/artfynd/A 12081-2024 artfynd.xlsx
@@ -1288,7 +1288,7 @@
         <v>74153941</v>
       </c>
       <c r="B7" t="n">
-        <v>104060</v>
+        <v>104087</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1399,7 +1399,7 @@
         <v>74116534</v>
       </c>
       <c r="B8" t="n">
-        <v>103682</v>
+        <v>103709</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1510,7 +1510,7 @@
         <v>74512145</v>
       </c>
       <c r="B9" t="n">
-        <v>105473</v>
+        <v>105501</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1621,7 +1621,7 @@
         <v>74566796</v>
       </c>
       <c r="B10" t="n">
-        <v>98615</v>
+        <v>98642</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1732,7 +1732,7 @@
         <v>75155258</v>
       </c>
       <c r="B11" t="n">
-        <v>101860</v>
+        <v>101887</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>

--- a/artfynd/A 12081-2024 artfynd.xlsx
+++ b/artfynd/A 12081-2024 artfynd.xlsx
@@ -1288,7 +1288,7 @@
         <v>74153941</v>
       </c>
       <c r="B7" t="n">
-        <v>104087</v>
+        <v>104093</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1399,7 +1399,7 @@
         <v>74116534</v>
       </c>
       <c r="B8" t="n">
-        <v>103709</v>
+        <v>103715</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1510,7 +1510,7 @@
         <v>74512145</v>
       </c>
       <c r="B9" t="n">
-        <v>105501</v>
+        <v>105507</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1621,7 +1621,7 @@
         <v>74566796</v>
       </c>
       <c r="B10" t="n">
-        <v>98642</v>
+        <v>98648</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1732,7 +1732,7 @@
         <v>75155258</v>
       </c>
       <c r="B11" t="n">
-        <v>101887</v>
+        <v>101893</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>

--- a/artfynd/A 12081-2024 artfynd.xlsx
+++ b/artfynd/A 12081-2024 artfynd.xlsx
@@ -1288,7 +1288,7 @@
         <v>74153941</v>
       </c>
       <c r="B7" t="n">
-        <v>104093</v>
+        <v>104100</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1399,7 +1399,7 @@
         <v>74116534</v>
       </c>
       <c r="B8" t="n">
-        <v>103715</v>
+        <v>103722</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1510,7 +1510,7 @@
         <v>74512145</v>
       </c>
       <c r="B9" t="n">
-        <v>105507</v>
+        <v>105514</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1621,7 +1621,7 @@
         <v>74566796</v>
       </c>
       <c r="B10" t="n">
-        <v>98648</v>
+        <v>98655</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1732,7 +1732,7 @@
         <v>75155258</v>
       </c>
       <c r="B11" t="n">
-        <v>101893</v>
+        <v>101900</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>

--- a/artfynd/A 12081-2024 artfynd.xlsx
+++ b/artfynd/A 12081-2024 artfynd.xlsx
@@ -1288,7 +1288,7 @@
         <v>74153941</v>
       </c>
       <c r="B7" t="n">
-        <v>104100</v>
+        <v>104104</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1399,7 +1399,7 @@
         <v>74116534</v>
       </c>
       <c r="B8" t="n">
-        <v>103722</v>
+        <v>103726</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1510,7 +1510,7 @@
         <v>74512145</v>
       </c>
       <c r="B9" t="n">
-        <v>105514</v>
+        <v>105518</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1621,7 +1621,7 @@
         <v>74566796</v>
       </c>
       <c r="B10" t="n">
-        <v>98655</v>
+        <v>98659</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1732,7 +1732,7 @@
         <v>75155258</v>
       </c>
       <c r="B11" t="n">
-        <v>101900</v>
+        <v>101904</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>

--- a/artfynd/A 12081-2024 artfynd.xlsx
+++ b/artfynd/A 12081-2024 artfynd.xlsx
@@ -1288,7 +1288,7 @@
         <v>74153941</v>
       </c>
       <c r="B7" t="n">
-        <v>104104</v>
+        <v>104111</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1399,7 +1399,7 @@
         <v>74116534</v>
       </c>
       <c r="B8" t="n">
-        <v>103726</v>
+        <v>103733</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1510,7 +1510,7 @@
         <v>74512145</v>
       </c>
       <c r="B9" t="n">
-        <v>105518</v>
+        <v>105525</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1621,7 +1621,7 @@
         <v>74566796</v>
       </c>
       <c r="B10" t="n">
-        <v>98659</v>
+        <v>98666</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1732,7 +1732,7 @@
         <v>75155258</v>
       </c>
       <c r="B11" t="n">
-        <v>101904</v>
+        <v>101911</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>

--- a/artfynd/A 12081-2024 artfynd.xlsx
+++ b/artfynd/A 12081-2024 artfynd.xlsx
@@ -1288,7 +1288,7 @@
         <v>74153941</v>
       </c>
       <c r="B7" t="n">
-        <v>104114</v>
+        <v>104119</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1399,7 +1399,7 @@
         <v>74116534</v>
       </c>
       <c r="B8" t="n">
-        <v>103736</v>
+        <v>103741</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1510,7 +1510,7 @@
         <v>74512145</v>
       </c>
       <c r="B9" t="n">
-        <v>105528</v>
+        <v>105533</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1621,7 +1621,7 @@
         <v>74566796</v>
       </c>
       <c r="B10" t="n">
-        <v>98669</v>
+        <v>98674</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1732,7 +1732,7 @@
         <v>75155258</v>
       </c>
       <c r="B11" t="n">
-        <v>101914</v>
+        <v>101919</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>

--- a/artfynd/A 12081-2024 artfynd.xlsx
+++ b/artfynd/A 12081-2024 artfynd.xlsx
@@ -1288,7 +1288,7 @@
         <v>74153941</v>
       </c>
       <c r="B7" t="n">
-        <v>104119</v>
+        <v>104127</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1399,7 +1399,7 @@
         <v>74116534</v>
       </c>
       <c r="B8" t="n">
-        <v>103741</v>
+        <v>103749</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1510,7 +1510,7 @@
         <v>74512145</v>
       </c>
       <c r="B9" t="n">
-        <v>105533</v>
+        <v>105541</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1621,7 +1621,7 @@
         <v>74566796</v>
       </c>
       <c r="B10" t="n">
-        <v>98674</v>
+        <v>98682</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1732,7 +1732,7 @@
         <v>75155258</v>
       </c>
       <c r="B11" t="n">
-        <v>101919</v>
+        <v>101927</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>

--- a/artfynd/A 12081-2024 artfynd.xlsx
+++ b/artfynd/A 12081-2024 artfynd.xlsx
@@ -1288,7 +1288,7 @@
         <v>74153941</v>
       </c>
       <c r="B7" t="n">
-        <v>104127</v>
+        <v>104137</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1399,7 +1399,7 @@
         <v>74116534</v>
       </c>
       <c r="B8" t="n">
-        <v>103749</v>
+        <v>103759</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1510,7 +1510,7 @@
         <v>74512145</v>
       </c>
       <c r="B9" t="n">
-        <v>105541</v>
+        <v>105551</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1621,7 +1621,7 @@
         <v>74566796</v>
       </c>
       <c r="B10" t="n">
-        <v>98682</v>
+        <v>98692</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1732,7 +1732,7 @@
         <v>75155258</v>
       </c>
       <c r="B11" t="n">
-        <v>101927</v>
+        <v>101937</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>

--- a/artfynd/A 12081-2024 artfynd.xlsx
+++ b/artfynd/A 12081-2024 artfynd.xlsx
@@ -675,37 +675,32 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>4021734</v>
+        <v>2300535</v>
       </c>
       <c r="B2" t="n">
-        <v>99565</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99142</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>221317</v>
+        <v>219847</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Gullklöver</t>
+          <t>Tvåblad</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Trifolium aureum</t>
+          <t>Neottia ovata</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>Pollich</t>
+          <t>(L.) Buff. &amp; Fingerh.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -715,10 +710,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>541883.140177156</v>
+        <v>541883</v>
       </c>
       <c r="R2" t="n">
-        <v>6409930.462705435</v>
+        <v>6409930</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -748,19 +743,9 @@
           <t>2002-08-10</t>
         </is>
       </c>
-      <c r="Z2" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA2" t="inlineStr">
         <is>
           <t>2002-08-10</t>
-        </is>
-      </c>
-      <c r="AB2" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AC2" t="inlineStr">
@@ -797,15 +782,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>4921855</v>
+        <v>74566796</v>
       </c>
       <c r="B3" t="n">
-        <v>101679</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99142</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -813,21 +793,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>222412</v>
+        <v>219847</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Tibast</t>
+          <t>Tvåblad</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Daphne mezereum</t>
+          <t>Neottia ovata</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(L.) Buff. &amp; Fingerh.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -837,13 +817,13 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>541883.140177156</v>
+        <v>541873</v>
       </c>
       <c r="R3" t="n">
-        <v>6409930.462705435</v>
+        <v>6409930</v>
       </c>
       <c r="S3" t="n">
-        <v>10</v>
+        <v>50</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -870,24 +850,14 @@
           <t>2002-08-10</t>
         </is>
       </c>
-      <c r="Z3" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA3" t="inlineStr">
         <is>
           <t>2002-08-10</t>
         </is>
       </c>
-      <c r="AB3" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AC3" t="inlineStr">
         <is>
-          <t>Smålands flora exkursion</t>
+          <t>Smålands flora 2007: KOO: 7F2i 1640. SOM: Listera ovata. LEG: Hans Thulin. KOM: Smålands flora exkursion</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -907,27 +877,26 @@
       <c r="AT3" t="inlineStr"/>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>Hans Thulin</t>
+          <t>Margareta Edqvist</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Hans Thulin</t>
-        </is>
-      </c>
-      <c r="AY3" t="inlineStr"/>
+          <t>Via Margareta Edqvist</t>
+        </is>
+      </c>
+      <c r="AY3" t="inlineStr">
+        <is>
+          <t>Smålands flora (1978-2007)</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>4884059</v>
+        <v>3330287</v>
       </c>
       <c r="B4" t="n">
-        <v>101322</v>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>106061</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -935,16 +904,16 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>222395</v>
+        <v>221101</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Dvärghäxört</t>
+          <t>Springkorn</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Circaea alpina</t>
+          <t>Impatiens noli-tangere</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
@@ -959,10 +928,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>541883.140177156</v>
+        <v>541883</v>
       </c>
       <c r="R4" t="n">
-        <v>6409930.462705435</v>
+        <v>6409930</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -992,19 +961,9 @@
           <t>2002-08-10</t>
         </is>
       </c>
-      <c r="Z4" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA4" t="inlineStr">
         <is>
           <t>2002-08-10</t>
-        </is>
-      </c>
-      <c r="AB4" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AC4" t="inlineStr">
@@ -1041,15 +1000,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>2300535</v>
+        <v>74512145</v>
       </c>
       <c r="B5" t="n">
-        <v>96355</v>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>106060</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1057,21 +1011,21 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>219847</v>
+        <v>221101</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Tvåblad</t>
+          <t>Springkorn</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Neottia ovata</t>
+          <t>Impatiens noli-tangere</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(L.) Buff. &amp; Fingerh.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1081,13 +1035,13 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>541883.140177156</v>
+        <v>541873</v>
       </c>
       <c r="R5" t="n">
-        <v>6409930.462705435</v>
+        <v>6409930</v>
       </c>
       <c r="S5" t="n">
-        <v>10</v>
+        <v>50</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -1114,24 +1068,14 @@
           <t>2002-08-10</t>
         </is>
       </c>
-      <c r="Z5" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA5" t="inlineStr">
         <is>
           <t>2002-08-10</t>
         </is>
       </c>
-      <c r="AB5" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AC5" t="inlineStr">
         <is>
-          <t>Smålands flora exkursion</t>
+          <t>Smålands flora 2007: KOO: 7F2i 1640. SOM: Impatiens noli-tangere. LEG: Hans Thulin. KOM: Smålands flora exkursion</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1151,49 +1095,48 @@
       <c r="AT5" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>Hans Thulin</t>
+          <t>Margareta Edqvist</t>
         </is>
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>Hans Thulin</t>
-        </is>
-      </c>
-      <c r="AY5" t="inlineStr"/>
+          <t>Via Margareta Edqvist</t>
+        </is>
+      </c>
+      <c r="AY5" t="inlineStr">
+        <is>
+          <t>Smålands flora (1978-2007)</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>3330287</v>
+        <v>4021734</v>
       </c>
       <c r="B6" t="n">
-        <v>103087</v>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>102419</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>221101</v>
+        <v>221317</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Springkorn</t>
+          <t>Gullklöver</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Impatiens noli-tangere</t>
+          <t>Trifolium aureum</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>Pollich</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1203,10 +1146,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>541883.140177156</v>
+        <v>541883</v>
       </c>
       <c r="R6" t="n">
-        <v>6409930.462705435</v>
+        <v>6409930</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1236,19 +1179,9 @@
           <t>2002-08-10</t>
         </is>
       </c>
-      <c r="Z6" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA6" t="inlineStr">
         <is>
           <t>2002-08-10</t>
-        </is>
-      </c>
-      <c r="AB6" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AC6" t="inlineStr">
@@ -1285,32 +1218,32 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>74153941</v>
+        <v>75155258</v>
       </c>
       <c r="B7" t="n">
-        <v>104137</v>
+        <v>102418</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>222412</v>
+        <v>221317</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Tibast</t>
+          <t>Gullklöver</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Daphne mezereum</t>
+          <t>Trifolium aureum</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>Pollich</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1360,7 +1293,7 @@
       </c>
       <c r="AC7" t="inlineStr">
         <is>
-          <t>Smålands flora 2007: KOO: 7F2i 1640. SOM: Daphne mezereum. LEG: Hans Thulin. KOM: Smålands flora exkursion</t>
+          <t>Smålands flora 2007: KOO: 7F2i 1640. SOM: Trifolium aureum. LEG: Hans Thulin. KOM: Smålands flora exkursion</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1396,10 +1329,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>74116534</v>
+        <v>4884059</v>
       </c>
       <c r="B8" t="n">
-        <v>103759</v>
+        <v>104253</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1431,13 +1364,13 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>541873</v>
+        <v>541883</v>
       </c>
       <c r="R8" t="n">
         <v>6409930</v>
       </c>
       <c r="S8" t="n">
-        <v>50</v>
+        <v>10</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
@@ -1471,7 +1404,7 @@
       </c>
       <c r="AC8" t="inlineStr">
         <is>
-          <t>Smålands flora 2007: KOO: 7F2i 1640. SOM: Circaea alpina. LEG: Hans Thulin. KOM: Smålands flora exkursion</t>
+          <t>Smålands flora exkursion</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1491,26 +1424,22 @@
       <c r="AT8" t="inlineStr"/>
       <c r="AW8" t="inlineStr">
         <is>
-          <t>Margareta Edqvist</t>
+          <t>Hans Thulin</t>
         </is>
       </c>
       <c r="AX8" t="inlineStr">
         <is>
-          <t>Via Margareta Edqvist</t>
-        </is>
-      </c>
-      <c r="AY8" t="inlineStr">
-        <is>
-          <t>Smålands flora (1978-2007)</t>
-        </is>
-      </c>
+          <t>Hans Thulin</t>
+        </is>
+      </c>
+      <c r="AY8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>74512145</v>
+        <v>74116534</v>
       </c>
       <c r="B9" t="n">
-        <v>105551</v>
+        <v>104252</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1518,16 +1447,16 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>221101</v>
+        <v>222395</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Springkorn</t>
+          <t>Dvärghäxört</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Impatiens noli-tangere</t>
+          <t>Circaea alpina</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
@@ -1582,7 +1511,7 @@
       </c>
       <c r="AC9" t="inlineStr">
         <is>
-          <t>Smålands flora 2007: KOO: 7F2i 1640. SOM: Impatiens noli-tangere. LEG: Hans Thulin. KOM: Smålands flora exkursion</t>
+          <t>Smålands flora 2007: KOO: 7F2i 1640. SOM: Circaea alpina. LEG: Hans Thulin. KOM: Smålands flora exkursion</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1618,10 +1547,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>74566796</v>
+        <v>4921855</v>
       </c>
       <c r="B10" t="n">
-        <v>98692</v>
+        <v>104628</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1629,21 +1558,21 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>219847</v>
+        <v>222412</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Tvåblad</t>
+          <t>Tibast</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Neottia ovata</t>
+          <t>Daphne mezereum</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(L.) Buff. &amp; Fingerh.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1653,13 +1582,13 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>541873</v>
+        <v>541883</v>
       </c>
       <c r="R10" t="n">
         <v>6409930</v>
       </c>
       <c r="S10" t="n">
-        <v>50</v>
+        <v>10</v>
       </c>
       <c r="T10" t="inlineStr">
         <is>
@@ -1693,7 +1622,7 @@
       </c>
       <c r="AC10" t="inlineStr">
         <is>
-          <t>Smålands flora 2007: KOO: 7F2i 1640. SOM: Listera ovata. LEG: Hans Thulin. KOM: Smålands flora exkursion</t>
+          <t>Smålands flora exkursion</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1713,48 +1642,44 @@
       <c r="AT10" t="inlineStr"/>
       <c r="AW10" t="inlineStr">
         <is>
-          <t>Margareta Edqvist</t>
+          <t>Hans Thulin</t>
         </is>
       </c>
       <c r="AX10" t="inlineStr">
         <is>
-          <t>Via Margareta Edqvist</t>
-        </is>
-      </c>
-      <c r="AY10" t="inlineStr">
-        <is>
-          <t>Smålands flora (1978-2007)</t>
-        </is>
-      </c>
+          <t>Hans Thulin</t>
+        </is>
+      </c>
+      <c r="AY10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>75155258</v>
+        <v>74153941</v>
       </c>
       <c r="B11" t="n">
-        <v>101937</v>
+        <v>104627</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>221317</v>
+        <v>222412</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Gullklöver</t>
+          <t>Tibast</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Trifolium aureum</t>
+          <t>Daphne mezereum</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>Pollich</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1804,7 +1729,7 @@
       </c>
       <c r="AC11" t="inlineStr">
         <is>
-          <t>Smålands flora 2007: KOO: 7F2i 1640. SOM: Trifolium aureum. LEG: Hans Thulin. KOM: Smålands flora exkursion</t>
+          <t>Smålands flora 2007: KOO: 7F2i 1640. SOM: Daphne mezereum. LEG: Hans Thulin. KOM: Smålands flora exkursion</t>
         </is>
       </c>
       <c r="AD11" t="b">

--- a/artfynd/A 12081-2024 artfynd.xlsx
+++ b/artfynd/A 12081-2024 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY11"/>
+  <dimension ref="A1:AZ11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -779,6 +784,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/2300535</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -890,6 +900,11 @@
           <t>Smålands flora (1978-2007)</t>
         </is>
       </c>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/74566796</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -997,6 +1012,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/3330287</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1108,6 +1128,11 @@
           <t>Smålands flora (1978-2007)</t>
         </is>
       </c>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/74512145</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1215,6 +1240,11 @@
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/4021734</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1326,6 +1356,11 @@
           <t>Smålands flora (1978-2007)</t>
         </is>
       </c>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/75155258</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -1433,6 +1468,11 @@
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/4884059</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -1544,6 +1584,11 @@
           <t>Smålands flora (1978-2007)</t>
         </is>
       </c>
+      <c r="AZ9" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/74116534</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -1651,6 +1696,11 @@
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
+      <c r="AZ10" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/4921855</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -1762,8 +1812,25 @@
           <t>Smålands flora (1978-2007)</t>
         </is>
       </c>
+      <c r="AZ11" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/74153941</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ9" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ10" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ11" r:id="rId10"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>